--- a/Data_Table/물건 테이블.xlsx
+++ b/Data_Table/물건 테이블.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Item" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Zone" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Furniture_Layout" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zone" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Furniture_Layout" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:U47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,9 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +540,21 @@
           <t>에셋</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>등장 층</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>해금 스킬 id (0 = 없음)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>사라지는 층 (0 = 계속)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -629,6 +647,21 @@
           <t>asset</t>
         </is>
       </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>from_floor</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>unlock_skill</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>to_floor</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -719,6 +752,21 @@
       <c r="R3" s="1" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -787,6 +835,15 @@
           <t>Items/item_flask</t>
         </is>
       </c>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -853,6 +910,15 @@
           <t>Items/item_erlen</t>
         </is>
       </c>
+      <c r="S5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -919,6 +985,15 @@
           <t>Items/item_beaker</t>
         </is>
       </c>
+      <c r="S6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -985,6 +1060,15 @@
           <t>Items/item_tuberack</t>
         </is>
       </c>
+      <c r="S7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1051,6 +1135,15 @@
           <t>Items/item_petri</t>
         </is>
       </c>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1113,6 +1206,15 @@
           <t>Items/item_pillbottle</t>
         </is>
       </c>
+      <c r="S9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1179,6 +1281,15 @@
           <t>Items/item_syringe</t>
         </is>
       </c>
+      <c r="S10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1241,6 +1352,15 @@
           <t>Items/item_clipboard</t>
         </is>
       </c>
+      <c r="S11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1307,6 +1427,15 @@
           <t>Items/item_mug</t>
         </is>
       </c>
+      <c r="S12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1369,6 +1498,15 @@
           <t>Items/item_goggles</t>
         </is>
       </c>
+      <c r="S13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1435,6 +1573,15 @@
           <t>Items/item_specimen</t>
         </is>
       </c>
+      <c r="S14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>92122</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1497,6 +1644,15 @@
           <t>Items/item_cage</t>
         </is>
       </c>
+      <c r="S15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1559,6 +1715,15 @@
           <t>Items/item_stool</t>
         </is>
       </c>
+      <c r="S16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1625,6 +1790,15 @@
           <t>Items/item_extinguisher</t>
         </is>
       </c>
+      <c r="S17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1691,6 +1865,15 @@
           <t>Items/item_watercooler</t>
         </is>
       </c>
+      <c r="S18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1753,6 +1936,15 @@
           <t>Items/item_firstaid</t>
         </is>
       </c>
+      <c r="S19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1815,6 +2007,15 @@
           <t>Items/item_microscope</t>
         </is>
       </c>
+      <c r="S20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>92222</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1881,6 +2082,15 @@
           <t>Items/item_biobin</t>
         </is>
       </c>
+      <c r="S21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1943,6 +2153,15 @@
           <t>Items/item_monitor</t>
         </is>
       </c>
+      <c r="S22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2005,6 +2224,15 @@
           <t>Items/item_centrifuge</t>
         </is>
       </c>
+      <c r="S23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>92322</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2067,6 +2295,15 @@
           <t>Items/item_cart</t>
         </is>
       </c>
+      <c r="S24" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2129,6 +2366,15 @@
           <t>Items/item_gastank</t>
         </is>
       </c>
+      <c r="S25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>92422</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2195,6 +2441,15 @@
           <t>Items/item_drum</t>
         </is>
       </c>
+      <c r="S26" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>92522</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2257,6 +2512,15 @@
           <t>Items/item_server</t>
         </is>
       </c>
+      <c r="S27" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>92622</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2319,6 +2583,15 @@
           <t>Furniture/furn_shelf</t>
         </is>
       </c>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2381,6 +2654,15 @@
           <t>Furniture/furn_bookshelf</t>
         </is>
       </c>
+      <c r="S29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2443,6 +2725,15 @@
           <t>Furniture/furn_cot</t>
         </is>
       </c>
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2505,6 +2796,15 @@
           <t>Furniture/furn_table</t>
         </is>
       </c>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2567,6 +2867,15 @@
           <t>Furniture/furn_chair</t>
         </is>
       </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2629,6 +2938,15 @@
           <t>Furniture/furn_desk</t>
         </is>
       </c>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2691,6 +3009,15 @@
           <t>Furniture/furn_locker</t>
         </is>
       </c>
+      <c r="S34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2753,6 +3080,15 @@
           <t>Furniture/furn_cabinet</t>
         </is>
       </c>
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2815,6 +3151,15 @@
           <t>Furniture/furn_sofa</t>
         </is>
       </c>
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2877,6 +3222,15 @@
           <t>Furniture/furn_fridge</t>
         </is>
       </c>
+      <c r="S37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2939,6 +3293,15 @@
           <t>Furniture/furn_vending</t>
         </is>
       </c>
+      <c r="S38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3004,6 +3367,595 @@
         <is>
           <t>Furniture/furn_plant</t>
         </is>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>60025</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>치즈 금고</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>cheesesafe</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1" t="n"/>
+      <c r="N40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_cheesesafe</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>92124</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>60026</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>황금 치즈 트로피</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>trophy</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1" t="n"/>
+      <c r="N41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_trophy</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>92224</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>60027</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>실험용 로봇 팔</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>robotarm</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1" t="n"/>
+      <c r="N42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_robotarm</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>92324</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>60028</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>냉동 수면 캡슐</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>cryopod</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1" t="inlineStr">
+        <is>
+          <t>#a9d3dc</t>
+        </is>
+      </c>
+      <c r="N43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_cryopod</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>92424</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>60029</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>거대 치즈 바퀴</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>cheesewheel</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1" t="inlineStr">
+        <is>
+          <t>#f2c14e</t>
+        </is>
+      </c>
+      <c r="N44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_cheesewheel</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>92524</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>60030</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>금괴 상자</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>goldcrate</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1" t="n"/>
+      <c r="N45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_goldcrate</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>92624</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>60031</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>데이터 코어</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>datacore</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1" t="inlineStr">
+        <is>
+          <t>#7fe0d0</t>
+        </is>
+      </c>
+      <c r="N46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_datacore</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>92724</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>60032</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>다이아몬드 치즈</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>cheesegem</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1" t="n"/>
+      <c r="N47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_cheesegem</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>92824</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3017,7 +3969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3066,71 +4018,6 @@
           <t>바닥 색조</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>물건_01</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>물건_02</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>물건_03</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>물건_04</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>물건_05</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>물건_06</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>물건_07</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>물건_08</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>물건_09</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>물건_10</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>물건_11</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>물건_12</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>물건_13</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -3158,71 +4045,6 @@
           <t>tint</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>item_01</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>item_02</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>item_03</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>item_04</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>item_05</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>item_06</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>item_07</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>item_08</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>item_09</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>item_10</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>item_11</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>item_12</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>item_13</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -3248,71 +4070,6 @@
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>string</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
@@ -3334,45 +4091,6 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="1" t="n">
-        <v>60001</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>60002</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>60003</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>60004</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>60005</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>60006</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>60007</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>60008</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>60009</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>60010</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>60011</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -3392,45 +4110,6 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="1" t="n">
-        <v>60001</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>60002</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>60003</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>60005</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>60007</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>60012</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>60013</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>60014</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>60015</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>60016</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>60017</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>60018</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>60011</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -3454,45 +4133,6 @@
           <t>rgba(157,213,168,.16)</t>
         </is>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>60002</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>60001</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>60006</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>60007</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>60017</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>60019</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>60020</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>60021</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>60022</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>60023</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>60004</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>60018</v>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -3516,45 +4156,6 @@
           <t>rgba(143,179,199,.2)</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>60019</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>60024</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>60021</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>60013</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>60015</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>60009</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>60008</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>60016</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>60014</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>60020</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -3577,45 +4178,6 @@
         <is>
           <t>rgba(227,196,106,.18)</t>
         </is>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>60019</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>60024</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>60023</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>60022</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>60020</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>60011</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>60009</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>60021</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>60017</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>60012</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/물건 테이블.xlsx
+++ b/Data_Table/물건 테이블.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2425,16 +2425,16 @@
         </is>
       </c>
       <c r="N26" s="1" t="n">
-        <v>0</v>
+        <v>60039</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>0</v>
+        <v>60039</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>0</v>
+        <v>60006</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0</v>
+        <v>60039</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
       </c>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="n">
-        <v>0</v>
+        <v>60037</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>0</v>
+        <v>60038</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>0</v>
+        <v>60038</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0</v>
+        <v>60037</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2638,16 +2638,16 @@
       </c>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="n">
-        <v>0</v>
+        <v>60042</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>0</v>
+        <v>60042</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>0</v>
+        <v>60043</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>0</v>
+        <v>60042</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
       </c>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="n">
-        <v>0</v>
+        <v>60045</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>0</v>
+        <v>60046</v>
       </c>
       <c r="P30" s="1" t="n">
         <v>0</v>
@@ -2780,13 +2780,13 @@
       </c>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="n">
-        <v>0</v>
+        <v>60009</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>0</v>
+        <v>60008</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>0</v>
+        <v>60048</v>
       </c>
       <c r="Q31" s="1" t="n">
         <v>0</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="n">
-        <v>0</v>
+        <v>60045</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>0</v>
@@ -2922,16 +2922,16 @@
       </c>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="n">
-        <v>0</v>
+        <v>60043</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>0</v>
+        <v>60044</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>0</v>
+        <v>60009</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>0</v>
+        <v>60042</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -2993,13 +2993,13 @@
       </c>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="n">
-        <v>0</v>
+        <v>60046</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>0</v>
+        <v>60010</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>0</v>
+        <v>60048</v>
       </c>
       <c r="Q34" s="1" t="n">
         <v>0</v>
@@ -3064,16 +3064,16 @@
       </c>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="n">
-        <v>0</v>
+        <v>60043</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>0</v>
+        <v>60043</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>0</v>
+        <v>60043</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>0</v>
+        <v>60042</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
       </c>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="n">
-        <v>0</v>
+        <v>60045</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>0</v>
+        <v>60045</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>0</v>
+        <v>60034</v>
       </c>
       <c r="Q36" s="1" t="n">
         <v>0</v>
@@ -3277,16 +3277,16 @@
       </c>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="n">
+        <v>60048</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>60048</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>60048</v>
+      </c>
+      <c r="Q38" s="1" t="n">
         <v>60009</v>
-      </c>
-      <c r="O38" s="1" t="n">
-        <v>60009</v>
-      </c>
-      <c r="P38" s="1" t="n">
-        <v>60006</v>
-      </c>
-      <c r="Q38" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="N39" s="1" t="n">
-        <v>0</v>
+        <v>60047</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>0</v>
@@ -3423,16 +3423,16 @@
       </c>
       <c r="M40" s="1" t="n"/>
       <c r="N40" s="1" t="n">
-        <v>0</v>
+        <v>60033</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>0</v>
+        <v>60033</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>0</v>
+        <v>60034</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>0</v>
+        <v>60036</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3565,13 +3565,13 @@
       </c>
       <c r="M42" s="1" t="n"/>
       <c r="N42" s="1" t="n">
-        <v>0</v>
+        <v>60041</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>0</v>
+        <v>60041</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>0</v>
+        <v>60038</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>0</v>
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="N43" s="1" t="n">
-        <v>0</v>
+        <v>60040</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>0</v>
+        <v>60040</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>0</v>
+        <v>60011</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>0</v>
+        <v>60040</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -3715,16 +3715,16 @@
         </is>
       </c>
       <c r="N44" s="1" t="n">
-        <v>0</v>
+        <v>60036</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>0</v>
+        <v>60036</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>0</v>
+        <v>60036</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>0</v>
+        <v>60036</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -3786,16 +3786,16 @@
       </c>
       <c r="M45" s="1" t="n"/>
       <c r="N45" s="1" t="n">
-        <v>0</v>
+        <v>60035</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>0</v>
+        <v>60035</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>0</v>
+        <v>60035</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>0</v>
+        <v>60034</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="N46" s="1" t="n">
-        <v>0</v>
+        <v>60038</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>0</v>
+        <v>60037</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>0</v>
+        <v>60038</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>0</v>
@@ -3955,6 +3955,1162 @@
         <v>92824</v>
       </c>
       <c r="U47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>지폐 다발</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1" t="n"/>
+      <c r="N48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_cash</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>동전 자루</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>coinbag</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1" t="n"/>
+      <c r="N49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_coinbag</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>금괴</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>goldbar</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1" t="n"/>
+      <c r="N50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_goldbar</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>치즈 조각</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>cheesewedge</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1" t="inlineStr">
+        <is>
+          <t>#f2d36b</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_cheesewedge</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>60037</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>하드디스크</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>harddisk</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1" t="n"/>
+      <c r="N52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_harddisk</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>60038</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>회로 기판</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>circuit</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1" t="n"/>
+      <c r="N53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_circuit</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>60039</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>약품 캔</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>chemcan</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1" t="inlineStr">
+        <is>
+          <t>#e8d36a</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_chemcan</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>60040</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>얼음 덩어리</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>ice</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1" t="inlineStr">
+        <is>
+          <t>#cfe8f5</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_ice</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>60041</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>톱니바퀴</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1" t="n"/>
+      <c r="N56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_gear</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>60042</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>두꺼운 책</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" s="1" t="n"/>
+      <c r="N57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_book</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>60043</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>서류 뭉치</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="1" t="n"/>
+      <c r="N58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_papers</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>60044</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>연필꽂이</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>pencilcup</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1" t="n"/>
+      <c r="N59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_pencilcup</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>60045</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>베개</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>pillow</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1" t="n"/>
+      <c r="N60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_pillow</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>60046</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>실험복</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>labcoat</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1" t="n"/>
+      <c r="N61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_labcoat</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60047</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>새싹 화분</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>sprout</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1" t="inlineStr">
+        <is>
+          <t>#8a6a4a</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_sprout</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>60048</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>캔 음료</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>soda</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>Spill</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1" t="inlineStr">
+        <is>
+          <t>#e07a6a</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Items/item_soda</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Data_Table/물건 테이블.xlsx
+++ b/Data_Table/물건 테이블.xlsx
@@ -423,12 +423,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U63"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -462,95 +462,100 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>물건 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>코드 id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>반지름</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>체력 배율</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>치즈 배율</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>출현 가중치</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>무게</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>큰 물건</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>튼튼함</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>종이류</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>얼룩 색</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>쏟아짐_01</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>쏟아짐_02</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>쏟아짐_03</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>쏟아짐_04</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>에셋</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>등장 층</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>해금 스킬 id (0 = 없음)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>사라지는 층 (0 = 계속)</t>
         </is>
@@ -569,95 +574,100 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>item_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>code_id</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>item_category</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>hp_mul</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>value_mul</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>spawn_weight</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>heavy</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>is_big</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>is_sturdy</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>is_paper</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>spill_color</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>drop_01</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>drop_02</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>drop_03</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>drop_04</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>asset</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>from_floor</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>unlock_skill</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>to_floor</t>
         </is>
@@ -676,95 +686,100 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="U3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -779,22 +794,22 @@
           <t>플라스크</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>2760001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>flask</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="F4" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
@@ -802,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>0</v>
@@ -813,14 +828,14 @@
       <c r="L4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>#9dd5a8</t>
         </is>
       </c>
-      <c r="N4" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" s="1" t="n">
         <v>0</v>
       </c>
@@ -830,18 +845,21 @@
       <c r="Q4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Items/item_flask</t>
         </is>
       </c>
-      <c r="S4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -854,30 +872,30 @@
           <t>삼각 플라스크</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>2760002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>erlen</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>1.1</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>0</v>
@@ -888,14 +906,14 @@
       <c r="L5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
         <is>
           <t>#e8a3a0</t>
         </is>
       </c>
-      <c r="N5" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" s="1" t="n">
         <v>0</v>
       </c>
@@ -905,18 +923,21 @@
       <c r="Q5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Items/item_erlen</t>
         </is>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -929,22 +950,22 @@
           <t>비커</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>2760003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>beaker</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="G6" s="1" t="n">
         <v>1</v>
       </c>
@@ -952,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>0</v>
@@ -963,14 +984,14 @@
       <c r="L6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="M6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
         <is>
           <t>#8fb3c7</t>
         </is>
       </c>
-      <c r="N6" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" s="1" t="n">
         <v>0</v>
       </c>
@@ -980,18 +1001,21 @@
       <c r="Q6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Items/item_beaker</t>
         </is>
       </c>
-      <c r="S6" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1004,30 +1028,30 @@
           <t>시험관 꽂이</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>2760004</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>tuberack</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>1.4</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>1.4</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>0</v>
@@ -1038,14 +1062,14 @@
       <c r="L7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>#e3c46a</t>
         </is>
       </c>
-      <c r="N7" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" s="1" t="n">
         <v>0</v>
       </c>
@@ -1055,18 +1079,21 @@
       <c r="Q7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Items/item_tuberack</t>
         </is>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1079,30 +1106,30 @@
           <t>페트리 접시</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>2760005</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>petri</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I8" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>0</v>
@@ -1113,14 +1140,14 @@
       <c r="L8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="M8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>#c9dba0</t>
         </is>
       </c>
-      <c r="N8" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" s="1" t="n">
         <v>0</v>
       </c>
@@ -1130,18 +1157,21 @@
       <c r="Q8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Items/item_petri</t>
         </is>
       </c>
-      <c r="S8" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1154,30 +1184,30 @@
           <t>약병</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>2760006</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>pillbottle</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>0</v>
@@ -1188,10 +1218,10 @@
       <c r="L9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="n">
         <v>0</v>
       </c>
@@ -1201,18 +1231,21 @@
       <c r="Q9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Items/item_pillbottle</t>
         </is>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="T9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1225,30 +1258,30 @@
           <t>주사기</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>2760007</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>syringe</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="F10" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>0</v>
@@ -1259,14 +1292,14 @@
       <c r="L10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="1" t="inlineStr">
+      <c r="M10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
         <is>
           <t>#8fb3c7</t>
         </is>
       </c>
-      <c r="N10" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" s="1" t="n">
         <v>0</v>
       </c>
@@ -1276,18 +1309,21 @@
       <c r="Q10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Items/item_syringe</t>
         </is>
       </c>
-      <c r="S10" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1300,44 +1336,44 @@
           <t>클립보드</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>2760008</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>clipboard</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="F11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="G11" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="H11" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I11" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="inlineStr"/>
       <c r="O11" s="1" t="n">
         <v>0</v>
       </c>
@@ -1347,18 +1383,21 @@
       <c r="Q11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Items/item_clipboard</t>
         </is>
       </c>
-      <c r="S11" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1371,22 +1410,22 @@
           <t>머그컵</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="n">
+        <v>2760009</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>mug</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="F12" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="G12" s="1" t="n">
         <v>1</v>
       </c>
@@ -1394,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>0</v>
@@ -1405,14 +1444,14 @@
       <c r="L12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="M12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>#6b3e1f</t>
         </is>
       </c>
-      <c r="N12" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" s="1" t="n">
         <v>0</v>
       </c>
@@ -1422,18 +1461,21 @@
       <c r="Q12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Items/item_mug</t>
         </is>
       </c>
-      <c r="S12" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1446,44 +1488,44 @@
           <t>보안경</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>2760010</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>goggles</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="F13" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="G13" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="H13" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I13" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="inlineStr"/>
       <c r="O13" s="1" t="n">
         <v>0</v>
       </c>
@@ -1493,18 +1535,21 @@
       <c r="Q13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Items/item_goggles</t>
         </is>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="T13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="T13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1517,30 +1562,30 @@
           <t>표본 병</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="2" t="n">
+        <v>2760011</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>specimen</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="F14" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="G14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="H14" s="1" t="n">
         <v>2.4</v>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I14" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>0</v>
@@ -1551,14 +1596,14 @@
       <c r="L14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="M14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
         <is>
           <t>#9dd5a8</t>
         </is>
       </c>
-      <c r="N14" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" s="1" t="n">
         <v>0</v>
       </c>
@@ -1568,18 +1613,21 @@
       <c r="Q14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Items/item_specimen</t>
         </is>
       </c>
-      <c r="S14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="n">
         <v>92122</v>
       </c>
-      <c r="U14" s="2" t="n">
+      <c r="V14" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1592,44 +1640,44 @@
           <t>케이지</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="2" t="n">
+        <v>2760012</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>cage</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="F15" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="G15" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="H15" s="1" t="n">
         <v>2.8</v>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I15" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="n">
         <v>0</v>
       </c>
@@ -1639,18 +1687,21 @@
       <c r="Q15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Items/item_cage</t>
         </is>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="T15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="T15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1663,44 +1714,44 @@
           <t>의자</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="2" t="n">
+        <v>2760013</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>stool</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="F16" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="G16" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="H16" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1" t="inlineStr"/>
-      <c r="N16" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="inlineStr"/>
       <c r="O16" s="1" t="n">
         <v>0</v>
       </c>
@@ -1710,18 +1761,21 @@
       <c r="Q16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Items/item_stool</t>
         </is>
       </c>
-      <c r="S16" s="2" t="n">
+      <c r="T16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="T16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1734,30 +1788,30 @@
           <t>소화기</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="2" t="n">
+        <v>2760014</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>extinguisher</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="F17" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="G17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="H17" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I17" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>0</v>
@@ -1768,14 +1822,14 @@
       <c r="L17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="M17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
         <is>
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="N17" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" s="1" t="n">
         <v>0</v>
       </c>
@@ -1785,18 +1839,21 @@
       <c r="Q17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>Items/item_extinguisher</t>
         </is>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="T17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="T17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1809,30 +1866,30 @@
           <t>정수기</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="2" t="n">
+        <v>2760015</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>watercooler</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="F18" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="G18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="H18" s="1" t="n">
         <v>2.6</v>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I18" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>0</v>
@@ -1843,14 +1900,14 @@
       <c r="L18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="1" t="inlineStr">
+      <c r="M18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
         <is>
           <t>#8fb3c7</t>
         </is>
       </c>
-      <c r="N18" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" s="1" t="n">
         <v>0</v>
       </c>
@@ -1860,18 +1917,21 @@
       <c r="Q18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Items/item_watercooler</t>
         </is>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="T18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1884,44 +1944,44 @@
           <t>구급상자</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="2" t="n">
+        <v>2760016</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>firstaid</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="F19" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>2</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1" t="inlineStr"/>
-      <c r="N19" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1" t="inlineStr"/>
       <c r="O19" s="1" t="n">
         <v>0</v>
       </c>
@@ -1931,18 +1991,21 @@
       <c r="Q19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>Items/item_firstaid</t>
         </is>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="T19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T19" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1955,44 +2018,44 @@
           <t>현미경</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" s="2" t="n">
+        <v>2760017</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>microscope</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="F20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="G20" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="H20" s="1" t="n">
         <v>2.4</v>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I20" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1" t="inlineStr"/>
       <c r="O20" s="1" t="n">
         <v>0</v>
       </c>
@@ -2002,18 +2065,21 @@
       <c r="Q20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="R20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Items/item_microscope</t>
         </is>
       </c>
-      <c r="S20" s="2" t="n">
+      <c r="T20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="U20" s="2" t="n">
         <v>92222</v>
       </c>
-      <c r="U20" s="2" t="n">
+      <c r="V20" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2026,48 +2092,48 @@
           <t>의료 폐기물통</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="2" t="n">
+        <v>2760018</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>biobin</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="F21" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="G21" s="1" t="n">
         <v>2.6</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="H21" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I21" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
         <is>
           <t>#c9dba0</t>
         </is>
       </c>
-      <c r="N21" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" s="1" t="n">
         <v>0</v>
       </c>
@@ -2077,18 +2143,21 @@
       <c r="Q21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Items/item_biobin</t>
         </is>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="T21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2101,44 +2170,44 @@
           <t>모니터</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" s="2" t="n">
+        <v>2760019</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>monitor</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="F22" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1" t="inlineStr"/>
       <c r="O22" s="1" t="n">
         <v>0</v>
       </c>
@@ -2148,18 +2217,21 @@
       <c r="Q22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>Items/item_monitor</t>
         </is>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="T22" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="T22" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2172,44 +2244,44 @@
           <t>원심분리기</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" s="2" t="n">
+        <v>2760020</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>centrifuge</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="F23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="G23" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="1" t="n">
+      <c r="H23" s="1" t="n">
         <v>3.6</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I23" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1" t="inlineStr"/>
-      <c r="N23" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1" t="inlineStr"/>
       <c r="O23" s="1" t="n">
         <v>0</v>
       </c>
@@ -2219,18 +2291,21 @@
       <c r="Q23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>Items/item_centrifuge</t>
         </is>
       </c>
-      <c r="S23" s="2" t="n">
+      <c r="T23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="U23" s="2" t="n">
         <v>92322</v>
       </c>
-      <c r="U23" s="2" t="n">
+      <c r="V23" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2243,44 +2318,44 @@
           <t>실험 카트</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C24" s="2" t="n">
+        <v>2760021</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>cart</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="F24" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="G24" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="1" t="n">
+      <c r="H24" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="I24" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="I24" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1" t="inlineStr"/>
       <c r="O24" s="1" t="n">
         <v>0</v>
       </c>
@@ -2290,18 +2365,21 @@
       <c r="Q24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>Items/item_cart</t>
         </is>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="T24" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2314,44 +2392,44 @@
           <t>가스통</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" s="2" t="n">
+        <v>2760022</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>gastank</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="F25" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="G25" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="1" t="n">
+      <c r="H25" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="I25" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="I25" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1" t="inlineStr"/>
       <c r="O25" s="1" t="n">
         <v>0</v>
       </c>
@@ -2361,18 +2439,21 @@
       <c r="Q25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>Items/item_gastank</t>
         </is>
       </c>
-      <c r="S25" s="2" t="n">
+      <c r="T25" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="U25" s="2" t="n">
         <v>92422</v>
       </c>
-      <c r="U25" s="2" t="n">
+      <c r="V25" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2385,69 +2466,72 @@
           <t>약품 드럼</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" s="2" t="n">
+        <v>2760023</v>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>drum</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="F26" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="G26" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="H26" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="I26" s="1" t="n">
         <v>0.45</v>
       </c>
-      <c r="I26" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1" t="inlineStr">
         <is>
           <t>#e3c46a</t>
         </is>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>60039</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>60039</v>
       </c>
       <c r="P26" s="1" t="n">
+        <v>60039</v>
+      </c>
+      <c r="Q26" s="1" t="n">
         <v>60006</v>
       </c>
-      <c r="Q26" s="1" t="n">
+      <c r="R26" s="1" t="n">
         <v>60039</v>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>Items/item_drum</t>
         </is>
       </c>
-      <c r="S26" s="2" t="n">
+      <c r="T26" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="T26" s="2" t="n">
+      <c r="U26" s="2" t="n">
         <v>92522</v>
       </c>
-      <c r="U26" s="2" t="n">
+      <c r="V26" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2460,65 +2544,68 @@
           <t>서버 랙</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C27" s="2" t="n">
+        <v>2760024</v>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>server</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="F27" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="G27" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="G27" s="1" t="n">
+      <c r="H27" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="I27" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="I27" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1" t="inlineStr"/>
+      <c r="O27" s="1" t="n">
         <v>60037</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>60038</v>
       </c>
       <c r="P27" s="1" t="n">
         <v>60038</v>
       </c>
       <c r="Q27" s="1" t="n">
+        <v>60038</v>
+      </c>
+      <c r="R27" s="1" t="n">
         <v>60037</v>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>Items/item_server</t>
         </is>
       </c>
-      <c r="S27" s="2" t="n">
+      <c r="T27" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="T27" s="2" t="n">
+      <c r="U27" s="2" t="n">
         <v>92622</v>
       </c>
-      <c r="U27" s="2" t="n">
+      <c r="V27" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2531,65 +2618,68 @@
           <t>선반</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" s="2" t="n">
+        <v>2761001</v>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>furn_shelf</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="F28" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="G28" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="G28" s="1" t="n">
+      <c r="H28" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J28" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1" t="inlineStr"/>
+      <c r="O28" s="1" t="n">
         <v>60001</v>
       </c>
-      <c r="O28" s="1" t="n">
+      <c r="P28" s="1" t="n">
         <v>60003</v>
       </c>
-      <c r="P28" s="1" t="n">
+      <c r="Q28" s="1" t="n">
         <v>60006</v>
       </c>
-      <c r="Q28" s="1" t="n">
+      <c r="R28" s="1" t="n">
         <v>60002</v>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_shelf</t>
         </is>
       </c>
-      <c r="S28" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2602,65 +2692,68 @@
           <t>책장</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C29" s="2" t="n">
+        <v>2761002</v>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>furn_bookshelf</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="F29" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F29" s="1" t="n">
+      <c r="G29" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="G29" s="1" t="n">
+      <c r="H29" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J29" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="n">
-        <v>60042</v>
-      </c>
+      <c r="M29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1" t="inlineStr"/>
       <c r="O29" s="1" t="n">
         <v>60042</v>
       </c>
       <c r="P29" s="1" t="n">
+        <v>60042</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>60043</v>
       </c>
-      <c r="Q29" s="1" t="n">
+      <c r="R29" s="1" t="n">
         <v>60042</v>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_bookshelf</t>
         </is>
       </c>
-      <c r="S29" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2673,65 +2766,68 @@
           <t>간이침대</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C30" s="2" t="n">
+        <v>2761003</v>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>furn_cot</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="F30" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="G30" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="G30" s="1" t="n">
+      <c r="H30" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J30" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1" t="inlineStr"/>
+      <c r="O30" s="1" t="n">
         <v>60045</v>
       </c>
-      <c r="O30" s="1" t="n">
+      <c r="P30" s="1" t="n">
         <v>60046</v>
       </c>
-      <c r="P30" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="Q30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_cot</t>
         </is>
       </c>
-      <c r="S30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2744,65 +2840,68 @@
           <t>탁자</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C31" s="2" t="n">
+        <v>2761004</v>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>furn_table</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="F31" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="G31" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="G31" s="1" t="n">
+      <c r="H31" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="H31" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J31" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1" t="inlineStr"/>
+      <c r="O31" s="1" t="n">
         <v>60009</v>
       </c>
-      <c r="O31" s="1" t="n">
+      <c r="P31" s="1" t="n">
         <v>60008</v>
       </c>
-      <c r="P31" s="1" t="n">
+      <c r="Q31" s="1" t="n">
         <v>60048</v>
       </c>
-      <c r="Q31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="R31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_table</t>
         </is>
       </c>
-      <c r="S31" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2815,65 +2914,68 @@
           <t>의자(가구)</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C32" s="2" t="n">
+        <v>2761005</v>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>furn_chair</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="F32" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="G32" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G32" s="1" t="n">
+      <c r="H32" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="J32" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1" t="inlineStr"/>
+      <c r="O32" s="1" t="n">
         <v>60045</v>
       </c>
-      <c r="O32" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="P32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_chair</t>
         </is>
       </c>
-      <c r="S32" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2886,65 +2988,68 @@
           <t>책상</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C33" s="2" t="n">
+        <v>2761006</v>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>furn_desk</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="F33" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="G33" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G33" s="1" t="n">
+      <c r="H33" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="H33" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J33" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="n">
+      <c r="M33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1" t="inlineStr"/>
+      <c r="O33" s="1" t="n">
         <v>60043</v>
       </c>
-      <c r="O33" s="1" t="n">
+      <c r="P33" s="1" t="n">
         <v>60044</v>
       </c>
-      <c r="P33" s="1" t="n">
+      <c r="Q33" s="1" t="n">
         <v>60009</v>
       </c>
-      <c r="Q33" s="1" t="n">
+      <c r="R33" s="1" t="n">
         <v>60042</v>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_desk</t>
         </is>
       </c>
-      <c r="S33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2957,65 +3062,68 @@
           <t>사물함</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" s="2" t="n">
+        <v>2761007</v>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
         <is>
           <t>furn_locker</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="F34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="G34" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="G34" s="1" t="n">
+      <c r="H34" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="H34" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J34" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1" t="inlineStr"/>
+      <c r="O34" s="1" t="n">
         <v>60046</v>
       </c>
-      <c r="O34" s="1" t="n">
+      <c r="P34" s="1" t="n">
         <v>60010</v>
       </c>
-      <c r="P34" s="1" t="n">
+      <c r="Q34" s="1" t="n">
         <v>60048</v>
       </c>
-      <c r="Q34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_locker</t>
         </is>
       </c>
-      <c r="S34" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3028,44 +3136,44 @@
           <t>서류함</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C35" s="2" t="n">
+        <v>2761008</v>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>furn_cabinet</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="F35" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="G35" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="G35" s="1" t="n">
+      <c r="H35" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H35" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J35" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="n">
-        <v>60043</v>
-      </c>
+      <c r="M35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1" t="inlineStr"/>
       <c r="O35" s="1" t="n">
         <v>60043</v>
       </c>
@@ -3073,20 +3181,23 @@
         <v>60043</v>
       </c>
       <c r="Q35" s="1" t="n">
+        <v>60043</v>
+      </c>
+      <c r="R35" s="1" t="n">
         <v>60042</v>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_cabinet</t>
         </is>
       </c>
-      <c r="S35" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3099,65 +3210,68 @@
           <t>소파</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C36" s="2" t="n">
+        <v>2761009</v>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>furn_sofa</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="F36" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="G36" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="G36" s="1" t="n">
+      <c r="H36" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="H36" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="n">
-        <v>60045</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1" t="inlineStr"/>
       <c r="O36" s="1" t="n">
         <v>60045</v>
       </c>
       <c r="P36" s="1" t="n">
+        <v>60045</v>
+      </c>
+      <c r="Q36" s="1" t="n">
         <v>60034</v>
       </c>
-      <c r="Q36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="R36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_sofa</t>
         </is>
       </c>
-      <c r="S36" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3170,65 +3284,68 @@
           <t>냉장고</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C37" s="2" t="n">
+        <v>2761010</v>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>furn_fridge</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="F37" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="G37" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="G37" s="1" t="n">
+      <c r="H37" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="H37" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J37" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1" t="inlineStr"/>
+      <c r="O37" s="1" t="n">
         <v>60011</v>
       </c>
-      <c r="O37" s="1" t="n">
+      <c r="P37" s="1" t="n">
         <v>60005</v>
       </c>
-      <c r="P37" s="1" t="n">
+      <c r="Q37" s="1" t="n">
         <v>60004</v>
       </c>
-      <c r="Q37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_fridge</t>
         </is>
       </c>
-      <c r="S37" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3241,44 +3358,44 @@
           <t>자판기</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C38" s="2" t="n">
+        <v>2761011</v>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>furn_vending</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="F38" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="G38" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="G38" s="1" t="n">
+      <c r="H38" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="H38" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="K38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="n">
-        <v>60048</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1" t="inlineStr"/>
       <c r="O38" s="1" t="n">
         <v>60048</v>
       </c>
@@ -3286,20 +3403,23 @@
         <v>60048</v>
       </c>
       <c r="Q38" s="1" t="n">
+        <v>60048</v>
+      </c>
+      <c r="R38" s="1" t="n">
         <v>60009</v>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_vending</t>
         </is>
       </c>
-      <c r="S38" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3312,69 +3432,72 @@
           <t>화분</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C39" s="2" t="n">
+        <v>2761012</v>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>furn_plant</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="F39" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="G39" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G39" s="1" t="n">
+      <c r="H39" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H39" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="J39" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1" t="inlineStr">
         <is>
           <t>#8a6a4a</t>
         </is>
       </c>
-      <c r="N39" s="1" t="n">
+      <c r="O39" s="1" t="n">
         <v>60047</v>
       </c>
-      <c r="O39" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R39" s="2" t="inlineStr">
+      <c r="R39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>Furniture/furn_plant</t>
         </is>
       </c>
-      <c r="S39" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3387,65 +3510,68 @@
           <t>치즈 금고</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C40" s="2" t="n">
+        <v>2760025</v>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
         <is>
           <t>cheesesafe</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="F40" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="G40" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G40" s="1" t="n">
+      <c r="H40" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="I40" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="I40" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1" t="n"/>
-      <c r="N40" s="1" t="n">
-        <v>60033</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1" t="n"/>
       <c r="O40" s="1" t="n">
         <v>60033</v>
       </c>
       <c r="P40" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="Q40" s="1" t="n">
         <v>60034</v>
       </c>
-      <c r="Q40" s="1" t="n">
+      <c r="R40" s="1" t="n">
         <v>60036</v>
       </c>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>Items/item_cheesesafe</t>
         </is>
       </c>
-      <c r="S40" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" s="2" t="n">
         <v>92124</v>
       </c>
-      <c r="U40" s="2" t="n">
+      <c r="V40" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3458,44 +3584,44 @@
           <t>황금 치즈 트로피</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C41" s="2" t="n">
+        <v>2760026</v>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>trophy</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="F41" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="G41" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="1" t="n">
+      <c r="H41" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H41" s="1" t="n">
+      <c r="I41" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="I41" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J41" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1" t="n"/>
-      <c r="N41" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1" t="n"/>
       <c r="O41" s="1" t="n">
         <v>0</v>
       </c>
@@ -3505,18 +3631,21 @@
       <c r="Q41" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="R41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>Items/item_trophy</t>
         </is>
       </c>
-      <c r="S41" s="2" t="n">
+      <c r="T41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="2" t="n">
+      <c r="U41" s="2" t="n">
         <v>92224</v>
       </c>
-      <c r="U41" s="2" t="n">
+      <c r="V41" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3529,65 +3658,68 @@
           <t>실험용 로봇 팔</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C42" s="2" t="n">
+        <v>2760027</v>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>robotarm</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="F42" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="G42" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G42" s="1" t="n">
+      <c r="H42" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="I42" s="1" t="n">
         <v>0.45</v>
       </c>
-      <c r="I42" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1" t="n"/>
-      <c r="N42" s="1" t="n">
-        <v>60041</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1" t="n"/>
       <c r="O42" s="1" t="n">
         <v>60041</v>
       </c>
       <c r="P42" s="1" t="n">
+        <v>60041</v>
+      </c>
+      <c r="Q42" s="1" t="n">
         <v>60038</v>
       </c>
-      <c r="Q42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="R42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>Items/item_robotarm</t>
         </is>
       </c>
-      <c r="S42" s="2" t="n">
+      <c r="T42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="T42" s="2" t="n">
+      <c r="U42" s="2" t="n">
         <v>92324</v>
       </c>
-      <c r="U42" s="2" t="n">
+      <c r="V42" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3600,69 +3732,72 @@
           <t>냉동 수면 캡슐</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C43" s="2" t="n">
+        <v>2760028</v>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>cryopod</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="F43" s="1" t="n">
         <v>28</v>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>14</v>
       </c>
       <c r="H43" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I43" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="I43" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="1" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1" t="inlineStr">
         <is>
           <t>#a9d3dc</t>
         </is>
-      </c>
-      <c r="N43" s="1" t="n">
-        <v>60040</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>60040</v>
       </c>
       <c r="P43" s="1" t="n">
+        <v>60040</v>
+      </c>
+      <c r="Q43" s="1" t="n">
         <v>60011</v>
       </c>
-      <c r="Q43" s="1" t="n">
+      <c r="R43" s="1" t="n">
         <v>60040</v>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>Items/item_cryopod</t>
         </is>
       </c>
-      <c r="S43" s="2" t="n">
+      <c r="T43" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T43" s="2" t="n">
+      <c r="U43" s="2" t="n">
         <v>92424</v>
       </c>
-      <c r="U43" s="2" t="n">
+      <c r="V43" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3675,47 +3810,47 @@
           <t>거대 치즈 바퀴</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C44" s="2" t="n">
+        <v>2760029</v>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>cheesewheel</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="F44" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="G44" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="G44" s="1" t="n">
+      <c r="H44" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="H44" s="1" t="n">
+      <c r="I44" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="I44" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1" t="inlineStr">
         <is>
           <t>#f2c14e</t>
         </is>
-      </c>
-      <c r="N44" s="1" t="n">
-        <v>60036</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>60036</v>
@@ -3726,18 +3861,21 @@
       <c r="Q44" s="1" t="n">
         <v>60036</v>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="R44" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>Items/item_cheesewheel</t>
         </is>
       </c>
-      <c r="S44" s="2" t="n">
+      <c r="T44" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="T44" s="2" t="n">
+      <c r="U44" s="2" t="n">
         <v>92524</v>
       </c>
-      <c r="U44" s="2" t="n">
+      <c r="V44" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3750,44 +3888,44 @@
           <t>금괴 상자</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C45" s="2" t="n">
+        <v>2760030</v>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>goldcrate</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="F45" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="F45" s="1" t="n">
+      <c r="G45" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="G45" s="1" t="n">
+      <c r="H45" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="H45" s="1" t="n">
+      <c r="I45" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="I45" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J45" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="1" t="n"/>
-      <c r="N45" s="1" t="n">
-        <v>60035</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1" t="n"/>
       <c r="O45" s="1" t="n">
         <v>60035</v>
       </c>
@@ -3795,20 +3933,23 @@
         <v>60035</v>
       </c>
       <c r="Q45" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R45" s="1" t="n">
         <v>60034</v>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>Items/item_goldcrate</t>
         </is>
       </c>
-      <c r="S45" s="2" t="n">
+      <c r="T45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="T45" s="2" t="n">
+      <c r="U45" s="2" t="n">
         <v>92624</v>
       </c>
-      <c r="U45" s="2" t="n">
+      <c r="V45" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3821,69 +3962,72 @@
           <t>데이터 코어</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C46" s="2" t="n">
+        <v>2760031</v>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>datacore</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="F46" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="G46" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G46" s="1" t="n">
+      <c r="H46" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="H46" s="1" t="n">
+      <c r="I46" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="I46" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="1" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1" t="inlineStr">
         <is>
           <t>#7fe0d0</t>
         </is>
       </c>
-      <c r="N46" s="1" t="n">
+      <c r="O46" s="1" t="n">
         <v>60038</v>
       </c>
-      <c r="O46" s="1" t="n">
+      <c r="P46" s="1" t="n">
         <v>60037</v>
       </c>
-      <c r="P46" s="1" t="n">
+      <c r="Q46" s="1" t="n">
         <v>60038</v>
       </c>
-      <c r="Q46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="R46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>Items/item_datacore</t>
         </is>
       </c>
-      <c r="S46" s="2" t="n">
+      <c r="T46" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="T46" s="2" t="n">
+      <c r="U46" s="2" t="n">
         <v>92724</v>
       </c>
-      <c r="U46" s="2" t="n">
+      <c r="V46" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3896,44 +4040,44 @@
           <t>다이아몬드 치즈</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C47" s="2" t="n">
+        <v>2760032</v>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>cheesegem</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="E47" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="F47" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F47" s="1" t="n">
+      <c r="G47" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="G47" s="1" t="n">
+      <c r="H47" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="H47" s="1" t="n">
+      <c r="I47" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="I47" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="1" t="n"/>
-      <c r="N47" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1" t="n"/>
       <c r="O47" s="1" t="n">
         <v>0</v>
       </c>
@@ -3943,18 +4087,21 @@
       <c r="Q47" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="R47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>Items/item_cheesegem</t>
         </is>
       </c>
-      <c r="S47" s="2" t="n">
+      <c r="T47" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="T47" s="2" t="n">
+      <c r="U47" s="2" t="n">
         <v>92824</v>
       </c>
-      <c r="U47" s="2" t="n">
+      <c r="V47" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3967,28 +4114,28 @@
           <t>지폐 다발</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C48" s="2" t="n">
+        <v>2760033</v>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="F48" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="G48" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="G48" s="1" t="n">
+      <c r="H48" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" s="1" t="n">
         <v>0</v>
       </c>
@@ -4001,10 +4148,10 @@
       <c r="L48" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="1" t="n"/>
-      <c r="N48" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1" t="n"/>
       <c r="O48" s="1" t="n">
         <v>0</v>
       </c>
@@ -4014,18 +4161,21 @@
       <c r="Q48" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="R48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>Items/item_cash</t>
         </is>
       </c>
-      <c r="S48" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4038,28 +4188,28 @@
           <t>동전 자루</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C49" s="2" t="n">
+        <v>2760034</v>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>coinbag</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="E49" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="F49" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="G49" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="G49" s="1" t="n">
+      <c r="H49" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="H49" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I49" s="1" t="n">
         <v>0</v>
       </c>
@@ -4072,10 +4222,10 @@
       <c r="L49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="1" t="n"/>
-      <c r="N49" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1" t="n"/>
       <c r="O49" s="1" t="n">
         <v>0</v>
       </c>
@@ -4085,18 +4235,21 @@
       <c r="Q49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="R49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
         <is>
           <t>Items/item_coinbag</t>
         </is>
       </c>
-      <c r="S49" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4109,28 +4262,28 @@
           <t>금괴</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C50" s="2" t="n">
+        <v>2760035</v>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
         <is>
           <t>goldbar</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="E50" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="F50" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="G50" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="G50" s="1" t="n">
+      <c r="H50" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H50" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I50" s="1" t="n">
         <v>0</v>
       </c>
@@ -4143,10 +4296,10 @@
       <c r="L50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="1" t="n"/>
-      <c r="N50" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1" t="n"/>
       <c r="O50" s="1" t="n">
         <v>0</v>
       </c>
@@ -4156,18 +4309,21 @@
       <c r="Q50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="R50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>Items/item_goldbar</t>
         </is>
       </c>
-      <c r="S50" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4180,28 +4336,28 @@
           <t>치즈 조각</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C51" s="2" t="n">
+        <v>2760036</v>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>cheesewedge</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="F51" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="G51" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="G51" s="1" t="n">
+      <c r="H51" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H51" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I51" s="1" t="n">
         <v>0</v>
       </c>
@@ -4214,14 +4370,14 @@
       <c r="L51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="1" t="inlineStr">
+      <c r="M51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1" t="inlineStr">
         <is>
           <t>#f2d36b</t>
         </is>
       </c>
-      <c r="N51" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O51" s="1" t="n">
         <v>0</v>
       </c>
@@ -4231,18 +4387,21 @@
       <c r="Q51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="R51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
         <is>
           <t>Items/item_cheesewedge</t>
         </is>
       </c>
-      <c r="S51" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4255,28 +4414,28 @@
           <t>하드디스크</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C52" s="2" t="n">
+        <v>2760037</v>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>harddisk</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="F52" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="G52" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="G52" s="1" t="n">
+      <c r="H52" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="H52" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I52" s="1" t="n">
         <v>0</v>
       </c>
@@ -4289,10 +4448,10 @@
       <c r="L52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M52" s="1" t="n"/>
-      <c r="N52" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1" t="n"/>
       <c r="O52" s="1" t="n">
         <v>0</v>
       </c>
@@ -4302,18 +4461,21 @@
       <c r="Q52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="R52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>Items/item_harddisk</t>
         </is>
       </c>
-      <c r="S52" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4326,28 +4488,28 @@
           <t>회로 기판</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C53" s="2" t="n">
+        <v>2760038</v>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>circuit</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="E53" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="F53" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="G53" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="G53" s="1" t="n">
+      <c r="H53" s="1" t="n">
         <v>1.1</v>
       </c>
-      <c r="H53" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I53" s="1" t="n">
         <v>0</v>
       </c>
@@ -4360,10 +4522,10 @@
       <c r="L53" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M53" s="1" t="n"/>
-      <c r="N53" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1" t="n"/>
       <c r="O53" s="1" t="n">
         <v>0</v>
       </c>
@@ -4373,18 +4535,21 @@
       <c r="Q53" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="R53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
         <is>
           <t>Items/item_circuit</t>
         </is>
       </c>
-      <c r="S53" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4397,27 +4562,27 @@
           <t>약품 캔</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C54" s="2" t="n">
+        <v>2760039</v>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
         <is>
           <t>chemcan</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="E54" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="F54" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="G54" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="G54" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="H54" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="1" t="n">
         <v>0</v>
@@ -4431,14 +4596,14 @@
       <c r="L54" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="1" t="inlineStr">
+      <c r="M54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1" t="inlineStr">
         <is>
           <t>#e8d36a</t>
         </is>
       </c>
-      <c r="N54" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O54" s="1" t="n">
         <v>0</v>
       </c>
@@ -4448,18 +4613,21 @@
       <c r="Q54" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="R54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
         <is>
           <t>Items/item_chemcan</t>
         </is>
       </c>
-      <c r="S54" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4472,28 +4640,28 @@
           <t>얼음 덩어리</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C55" s="2" t="n">
+        <v>2760040</v>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>ice</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr">
+      <c r="E55" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="F55" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="G55" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="G55" s="1" t="n">
+      <c r="H55" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="H55" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I55" s="1" t="n">
         <v>0</v>
       </c>
@@ -4506,14 +4674,14 @@
       <c r="L55" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M55" s="1" t="inlineStr">
+      <c r="M55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
         <is>
           <t>#cfe8f5</t>
         </is>
       </c>
-      <c r="N55" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O55" s="1" t="n">
         <v>0</v>
       </c>
@@ -4523,18 +4691,21 @@
       <c r="Q55" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="R55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
         <is>
           <t>Items/item_ice</t>
         </is>
       </c>
-      <c r="S55" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4547,27 +4718,27 @@
           <t>톱니바퀴</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C56" s="2" t="n">
+        <v>2760041</v>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
         <is>
           <t>gear</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr">
+      <c r="E56" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="F56" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="G56" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="G56" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="H56" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="1" t="n">
         <v>0</v>
@@ -4581,10 +4752,10 @@
       <c r="L56" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M56" s="1" t="n"/>
-      <c r="N56" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1" t="n"/>
       <c r="O56" s="1" t="n">
         <v>0</v>
       </c>
@@ -4594,18 +4765,21 @@
       <c r="Q56" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="R56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
         <is>
           <t>Items/item_gear</t>
         </is>
       </c>
-      <c r="S56" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4618,28 +4792,28 @@
           <t>두꺼운 책</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C57" s="2" t="n">
+        <v>2760042</v>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="E57" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="F57" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F57" s="1" t="n">
+      <c r="G57" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="G57" s="1" t="n">
+      <c r="H57" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="H57" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I57" s="1" t="n">
         <v>0</v>
       </c>
@@ -4650,12 +4824,12 @@
         <v>0</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" s="1" t="n"/>
-      <c r="N57" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="1" t="n"/>
       <c r="O57" s="1" t="n">
         <v>0</v>
       </c>
@@ -4665,18 +4839,21 @@
       <c r="Q57" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="R57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
         <is>
           <t>Items/item_book</t>
         </is>
       </c>
-      <c r="S57" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4689,28 +4866,28 @@
           <t>서류 뭉치</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C58" s="2" t="n">
+        <v>2760043</v>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
         <is>
           <t>papers</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="F58" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="G58" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="G58" s="1" t="n">
+      <c r="H58" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="H58" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I58" s="1" t="n">
         <v>0</v>
       </c>
@@ -4721,12 +4898,12 @@
         <v>0</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" s="1" t="n"/>
-      <c r="N58" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="1" t="n"/>
       <c r="O58" s="1" t="n">
         <v>0</v>
       </c>
@@ -4736,18 +4913,21 @@
       <c r="Q58" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="R58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>Items/item_papers</t>
         </is>
       </c>
-      <c r="S58" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4760,28 +4940,28 @@
           <t>연필꽂이</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C59" s="2" t="n">
+        <v>2760044</v>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>pencilcup</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="F59" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="G59" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="H59" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="H59" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I59" s="1" t="n">
         <v>0</v>
       </c>
@@ -4794,10 +4974,10 @@
       <c r="L59" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M59" s="1" t="n"/>
-      <c r="N59" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1" t="n"/>
       <c r="O59" s="1" t="n">
         <v>0</v>
       </c>
@@ -4807,18 +4987,21 @@
       <c r="Q59" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="R59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
         <is>
           <t>Items/item_pencilcup</t>
         </is>
       </c>
-      <c r="S59" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4831,28 +5014,28 @@
           <t>베개</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C60" s="2" t="n">
+        <v>2760045</v>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
         <is>
           <t>pillow</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr">
+      <c r="E60" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="F60" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="G60" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="G60" s="1" t="n">
+      <c r="H60" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="H60" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I60" s="1" t="n">
         <v>0</v>
       </c>
@@ -4865,10 +5048,10 @@
       <c r="L60" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M60" s="1" t="n"/>
-      <c r="N60" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1" t="n"/>
       <c r="O60" s="1" t="n">
         <v>0</v>
       </c>
@@ -4878,18 +5061,21 @@
       <c r="Q60" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="R60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>Items/item_pillow</t>
         </is>
       </c>
-      <c r="S60" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4902,28 +5088,28 @@
           <t>실험복</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C61" s="2" t="n">
+        <v>2760046</v>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
         <is>
           <t>labcoat</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="E61" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="F61" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F61" s="1" t="n">
+      <c r="G61" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="G61" s="1" t="n">
+      <c r="H61" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="H61" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I61" s="1" t="n">
         <v>0</v>
       </c>
@@ -4936,10 +5122,10 @@
       <c r="L61" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M61" s="1" t="n"/>
-      <c r="N61" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1" t="n"/>
       <c r="O61" s="1" t="n">
         <v>0</v>
       </c>
@@ -4949,18 +5135,21 @@
       <c r="Q61" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="R61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
         <is>
           <t>Items/item_labcoat</t>
         </is>
       </c>
-      <c r="S61" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4973,27 +5162,27 @@
           <t>새싹 화분</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C62" s="2" t="n">
+        <v>2760047</v>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
         <is>
           <t>sprout</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr">
+      <c r="E62" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="F62" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F62" s="1" t="n">
+      <c r="G62" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="G62" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="H62" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>0</v>
@@ -5007,14 +5196,14 @@
       <c r="L62" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M62" s="1" t="inlineStr">
+      <c r="M62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
         <is>
           <t>#8a6a4a</t>
         </is>
       </c>
-      <c r="N62" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O62" s="1" t="n">
         <v>0</v>
       </c>
@@ -5024,18 +5213,21 @@
       <c r="Q62" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="R62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
         <is>
           <t>Items/item_sprout</t>
         </is>
       </c>
-      <c r="S62" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5048,27 +5240,27 @@
           <t>캔 음료</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C63" s="2" t="n">
+        <v>2760048</v>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>soda</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="E63" s="1" t="inlineStr">
         <is>
           <t>Spill</t>
         </is>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="F63" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="G63" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="G63" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="H63" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>0</v>
@@ -5082,14 +5274,14 @@
       <c r="L63" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M63" s="1" t="inlineStr">
+      <c r="M63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
         <is>
           <t>#e07a6a</t>
         </is>
       </c>
-      <c r="N63" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O63" s="1" t="n">
         <v>0</v>
       </c>
@@ -5099,18 +5291,21 @@
       <c r="Q63" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R63" s="2" t="inlineStr">
+      <c r="R63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
         <is>
           <t>Items/item_soda</t>
         </is>
       </c>
-      <c r="S63" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5125,12 +5320,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -5161,15 +5356,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>구간 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>시작 층</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>바닥 종류</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>바닥 색조</t>
         </is>
@@ -5188,15 +5388,20 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>zone_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>from_floor</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>floor_type</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>tint</t>
         </is>
@@ -5220,10 +5425,15 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -5238,15 +5448,18 @@
           <t>지하 비밀 실험실</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>2870001</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -5257,15 +5470,18 @@
           <t>실험동물 사육동</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
+        <v>2870002</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Corridor</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -5276,15 +5492,18 @@
           <t>약품 연구동</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
+        <v>2870003</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>rgba(157,213,168,.16)</t>
         </is>
@@ -5299,15 +5518,18 @@
           <t>전산·관리동</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
+        <v>2870004</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Corridor</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>rgba(143,179,199,.2)</t>
         </is>
@@ -5322,15 +5544,18 @@
           <t>연구소장 층</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
+        <v>2870005</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>rgba(227,196,106,.18)</t>
         </is>

--- a/Data_Table/물건 테이블.xlsx
+++ b/Data_Table/물건 테이블.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -1628,7 +1628,7 @@
         <v>92122</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -2080,7 +2080,7 @@
         <v>92222</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -2306,7 +2306,7 @@
         <v>92322</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -2380,7 +2380,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -2454,7 +2454,7 @@
         <v>92422</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -2532,7 +2532,7 @@
         <v>92522</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -2606,7 +2606,7 @@
         <v>92622</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -5306,6 +5306,8094 @@
         <v>0</v>
       </c>
       <c r="V63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62101</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>실뭉치</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>2762101</v>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>yarn</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>#f2d6a0</t>
+        </is>
+      </c>
+      <c r="O64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/yarn</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>62102</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>츄르 상자</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>2762102</v>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>churu_box</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1" t="n"/>
+      <c r="O65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/churu_box</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>62103</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>스크래처</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>2762103</v>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>scratcher</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="G66" s="1" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1" t="n"/>
+      <c r="O66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/scratcher</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>62104</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>오이</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>2762104</v>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t>#f2d6a0</t>
+        </is>
+      </c>
+      <c r="O67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/cucumber</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>62105</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>깃털 낚싯대</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>2762105</v>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>feather_wand</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1" t="n"/>
+      <c r="O68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/feather_wand</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>62106</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>발자국 비커</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>2762106</v>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>paw_beaker</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G69" s="1" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1" t="n"/>
+      <c r="O69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/paw_beaker</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>62107</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ffff 노트북</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>2762107</v>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>cat_laptop</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G70" s="1" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t>#f2d6a0</t>
+        </is>
+      </c>
+      <c r="O70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/cat_laptop</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>62108</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>딱 맞는 빈 박스</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>2762108</v>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>cat_box</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G71" s="1" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1" t="n"/>
+      <c r="O71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/cat_box</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>62109</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>구멍 난 식빵</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>2762109</v>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>cat_bread</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G72" s="1" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1" t="n"/>
+      <c r="O72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/cat_bread</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>62110</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>넘어진 꽃병</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>2762110</v>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>tipped_vase</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G73" s="1" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>#f2d6a0</t>
+        </is>
+      </c>
+      <c r="O73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/tipped_vase</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>62111</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>황금 츄르</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>2762111</v>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>golden_churu</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G74" s="1" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="1" t="n"/>
+      <c r="O74" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q74" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R74" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/golden_churu</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>62112</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>고양이는 액체다 병</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>2762112</v>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>liquid_cat</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1" t="n"/>
+      <c r="O75" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q75" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R75" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/liquid_cat</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>62113</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>냥캣 토스트</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>2762113</v>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>nyan_toast</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G76" s="1" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1" t="n"/>
+      <c r="O76" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q76" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R76" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/nyan_toast</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>63101</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>대형 캣타워</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>2763101</v>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>f_cat_tower</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="G77" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1" t="n"/>
+      <c r="O77" s="1" t="n">
+        <v>62101</v>
+      </c>
+      <c r="P77" s="1" t="n">
+        <v>62104</v>
+      </c>
+      <c r="Q77" s="1" t="n">
+        <v>62108</v>
+      </c>
+      <c r="R77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_cat_tower</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>63102</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>샐러드 식탁</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>2763102</v>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>f_salad_table</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1" t="n"/>
+      <c r="O78" s="1" t="n">
+        <v>62103</v>
+      </c>
+      <c r="P78" s="1" t="n">
+        <v>62106</v>
+      </c>
+      <c r="Q78" s="1" t="n">
+        <v>62110</v>
+      </c>
+      <c r="R78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_salad_table</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>63103</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>펫 이동장</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>2763103</v>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>f_pet_carrier</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="G79" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1" t="n"/>
+      <c r="O79" s="1" t="n">
+        <v>62105</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>62108</v>
+      </c>
+      <c r="Q79" s="1" t="n">
+        <v>62102</v>
+      </c>
+      <c r="R79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_pet_carrier</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>63104</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>츄르 자판기</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>2763104</v>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>f_churu_vending</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1" t="n"/>
+      <c r="O80" s="1" t="n">
+        <v>62107</v>
+      </c>
+      <c r="P80" s="1" t="n">
+        <v>62110</v>
+      </c>
+      <c r="Q80" s="1" t="n">
+        <v>62104</v>
+      </c>
+      <c r="R80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_churu_vending</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>63105</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>봉고 드럼 책상</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>2763105</v>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>f_bongo_desk</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="G81" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1" t="n"/>
+      <c r="O81" s="1" t="n">
+        <v>62109</v>
+      </c>
+      <c r="P81" s="1" t="n">
+        <v>62102</v>
+      </c>
+      <c r="Q81" s="1" t="n">
+        <v>62106</v>
+      </c>
+      <c r="R81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_bongo_desk</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>62201</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>암모나이트</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>2762201</v>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>ammonite</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="1" t="inlineStr">
+        <is>
+          <t>#c9a26b</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/ammonite</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>62202</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>삼엽충 화석</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>2762202</v>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>trilobite</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="1" t="n"/>
+      <c r="O83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/trilobite</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>62203</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>발자국 석고본</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>2762203</v>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>footprint_cast</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="1" t="n"/>
+      <c r="O84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/footprint_cast</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>62204</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>평평한 지구본</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>2762204</v>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>flat_earth</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="1" t="inlineStr">
+        <is>
+          <t>#c9a26b</t>
+        </is>
+      </c>
+      <c r="O85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/flat_earth</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>62205</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>발굴용 곡괭이</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>2762205</v>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>pickaxe</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="1" t="n"/>
+      <c r="O86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/pickaxe</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>62206</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>호박 속 모기</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>2762206</v>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>amber_mosquito</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="1" t="n"/>
+      <c r="O87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/amber_mosquito</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>62207</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>공룡알</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>2762207</v>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>dino_egg</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1" t="inlineStr">
+        <is>
+          <t>#c9a26b</t>
+        </is>
+      </c>
+      <c r="O88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/dino_egg</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>62208</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>오프라인 공룡 모니터</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>2762208</v>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>offline_dino</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="1" t="n"/>
+      <c r="O89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/offline_dino</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>62209</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>공룡 너겟</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>2762209</v>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>dino_nuggets</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="1" t="n"/>
+      <c r="O90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/dino_nuggets</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>62210</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>공룡 머리 화석</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>2762210</v>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>raptor_skull</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="1" t="inlineStr">
+        <is>
+          <t>#c9a26b</t>
+        </is>
+      </c>
+      <c r="O91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/raptor_skull</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>62211</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>황금 공룡알</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>2762211</v>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>golden_egg</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1" t="n"/>
+      <c r="O92" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P92" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q92" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R92" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/golden_egg</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>62212</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>금괴 박힌 호박</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>2762212</v>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>amber_gold</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H93" s="1" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="1" t="n"/>
+      <c r="O93" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P93" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q93" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R93" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/amber_gold</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>62213</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>불타는 운석</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>2762213</v>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>meteorite</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H94" s="1" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1" t="n"/>
+      <c r="O94" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P94" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q94" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R94" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/meteorite</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>63201</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>티렉스 화석</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>2763201</v>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>f_trex</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H95" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="1" t="n"/>
+      <c r="O95" s="1" t="n">
+        <v>62201</v>
+      </c>
+      <c r="P95" s="1" t="n">
+        <v>62204</v>
+      </c>
+      <c r="Q95" s="1" t="n">
+        <v>62208</v>
+      </c>
+      <c r="R95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_trex</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>63202</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>유리 진열장</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>2763202</v>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>f_display_case</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H96" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="1" t="n"/>
+      <c r="O96" s="1" t="n">
+        <v>62203</v>
+      </c>
+      <c r="P96" s="1" t="n">
+        <v>62206</v>
+      </c>
+      <c r="Q96" s="1" t="n">
+        <v>62210</v>
+      </c>
+      <c r="R96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_display_case</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>63203</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>발굴 작업대</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>2763203</v>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>f_dig_table</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H97" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="1" t="n"/>
+      <c r="O97" s="1" t="n">
+        <v>62205</v>
+      </c>
+      <c r="P97" s="1" t="n">
+        <v>62208</v>
+      </c>
+      <c r="Q97" s="1" t="n">
+        <v>62202</v>
+      </c>
+      <c r="R97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_dig_table</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>63204</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>연구원 책상</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>2763204</v>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>f_research_desk</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H98" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="1" t="n"/>
+      <c r="O98" s="1" t="n">
+        <v>62207</v>
+      </c>
+      <c r="P98" s="1" t="n">
+        <v>62210</v>
+      </c>
+      <c r="Q98" s="1" t="n">
+        <v>62204</v>
+      </c>
+      <c r="R98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_research_desk</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>63205</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>매점 카운터</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>2763205</v>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>f_snack_counter</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H99" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="1" t="n"/>
+      <c r="O99" s="1" t="n">
+        <v>62209</v>
+      </c>
+      <c r="P99" s="1" t="n">
+        <v>62202</v>
+      </c>
+      <c r="Q99" s="1" t="n">
+        <v>62206</v>
+      </c>
+      <c r="R99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_snack_counter</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>62301</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>조아쓰 안전모</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>2762301</v>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>joassu_helmet</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1" t="inlineStr">
+        <is>
+          <t>#9a9a9a</t>
+        </is>
+      </c>
+      <c r="O100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/joassu_helmet</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>62302</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>러버콘</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>2762302</v>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>rubber_cone</t>
+        </is>
+      </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="1" t="n"/>
+      <c r="O101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/rubber_cone</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>62303</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>시멘트 포대</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>2762303</v>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>cement_bag</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H102" s="1" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="1" t="n"/>
+      <c r="O102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/cement_bag</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>62304</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>찌그러진 양은냄비</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>2762304</v>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>yangeun_pot</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H103" s="1" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="1" t="inlineStr">
+        <is>
+          <t>#9a9a9a</t>
+        </is>
+      </c>
+      <c r="O103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/yangeun_pot</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>62305</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>외발 수레</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>2762305</v>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>wheelbarrow</t>
+        </is>
+      </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H104" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="1" t="n"/>
+      <c r="O104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/wheelbarrow</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>62306</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>목장갑</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>2762306</v>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>work_gloves</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G105" s="1" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H105" s="1" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="1" t="n"/>
+      <c r="O105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/work_gloves</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>62307</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>철근 다발</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>2762307</v>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>rebar_bundle</t>
+        </is>
+      </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H106" s="1" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I106" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="1" t="inlineStr">
+        <is>
+          <t>#9a9a9a</t>
+        </is>
+      </c>
+      <c r="O106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/rebar_bundle</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>62308</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>믹스커피 상자</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>2762308</v>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>coffee_mix</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G107" s="1" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H107" s="1" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="1" t="n"/>
+      <c r="O107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/coffee_mix</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>62309</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>무재해 0일 표지판</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>2762309</v>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>zero_days_sign</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H108" s="1" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" s="1" t="n"/>
+      <c r="O108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/zero_days_sign</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>62310</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>시바견 안전 포스터</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>2762310</v>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>doge_poster</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G109" s="1" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H109" s="1" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" s="1" t="inlineStr">
+        <is>
+          <t>#9a9a9a</t>
+        </is>
+      </c>
+      <c r="O109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/doge_poster</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>62311</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>기공식 황금 삽</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>2762311</v>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>golden_shovel</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H110" s="1" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="1" t="n"/>
+      <c r="O110" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P110" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q110" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R110" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/golden_shovel</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>62312</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>황금 쥐 장식</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>2762312</v>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>golden_rat</t>
+        </is>
+      </c>
+      <c r="E111" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G111" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="H111" s="1" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="1" t="n"/>
+      <c r="O111" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P111" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q111" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R111" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/golden_rat</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>62313</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>두툼한 월급봉투</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>2762313</v>
+      </c>
+      <c r="D112" s="1" t="inlineStr">
+        <is>
+          <t>pay_envelope</t>
+        </is>
+      </c>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G112" s="1" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H112" s="1" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="1" t="n"/>
+      <c r="O112" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P112" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q112" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R112" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/pay_envelope</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>63301</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>불타는 현장 책상</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>2763301</v>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t>f_this_is_fine</t>
+        </is>
+      </c>
+      <c r="E113" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="G113" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H113" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="1" t="n"/>
+      <c r="O113" s="1" t="n">
+        <v>62301</v>
+      </c>
+      <c r="P113" s="1" t="n">
+        <v>62304</v>
+      </c>
+      <c r="Q113" s="1" t="n">
+        <v>62308</v>
+      </c>
+      <c r="R113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_this_is_fine</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>63302</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>비계</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>2763302</v>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>f_scaffold</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="G114" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H114" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="1" t="n"/>
+      <c r="O114" s="1" t="n">
+        <v>62303</v>
+      </c>
+      <c r="P114" s="1" t="n">
+        <v>62306</v>
+      </c>
+      <c r="Q114" s="1" t="n">
+        <v>62310</v>
+      </c>
+      <c r="R114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_scaffold</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>63303</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>자재 팔레트</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>2763303</v>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>f_pallet</t>
+        </is>
+      </c>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="G115" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H115" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="1" t="n"/>
+      <c r="O115" s="1" t="n">
+        <v>62305</v>
+      </c>
+      <c r="P115" s="1" t="n">
+        <v>62308</v>
+      </c>
+      <c r="Q115" s="1" t="n">
+        <v>62302</v>
+      </c>
+      <c r="R115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_pallet</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>63304</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>미니 포크레인</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>2763304</v>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>f_mini_excavator</t>
+        </is>
+      </c>
+      <c r="E116" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H116" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K116" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="1" t="n"/>
+      <c r="O116" s="1" t="n">
+        <v>62307</v>
+      </c>
+      <c r="P116" s="1" t="n">
+        <v>62310</v>
+      </c>
+      <c r="Q116" s="1" t="n">
+        <v>62304</v>
+      </c>
+      <c r="R116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_mini_excavator</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>63305</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>함바 식판 수레</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>2763305</v>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>f_tray_cart</t>
+        </is>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="G117" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H117" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="1" t="n"/>
+      <c r="O117" s="1" t="n">
+        <v>62309</v>
+      </c>
+      <c r="P117" s="1" t="n">
+        <v>62302</v>
+      </c>
+      <c r="Q117" s="1" t="n">
+        <v>62306</v>
+      </c>
+      <c r="R117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_tray_cart</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>62401</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>산호 조각</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>2762401</v>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>coral</t>
+        </is>
+      </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G118" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H118" s="1" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I118" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="1" t="inlineStr">
+        <is>
+          <t>#8fd3e8</t>
+        </is>
+      </c>
+      <c r="O118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/coral</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>62402</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>불가사리</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>2762402</v>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>starfish</t>
+        </is>
+      </c>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G119" s="1" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H119" s="1" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I119" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="1" t="n"/>
+      <c r="O119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/starfish</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>62403</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>소라</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>2762403</v>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>conch</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H120" s="1" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I120" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="1" t="n"/>
+      <c r="O120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/conch</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>62404</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>문어 항아리</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>2762404</v>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>octopus_pot</t>
+        </is>
+      </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G121" s="1" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H121" s="1" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I121" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="1" t="inlineStr">
+        <is>
+          <t>#8fd3e8</t>
+        </is>
+      </c>
+      <c r="O121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/octopus_pot</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>62405</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>광어 스티로폼 박스</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>2762405</v>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>flatfish_box</t>
+        </is>
+      </c>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G122" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H122" s="1" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I122" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="1" t="n"/>
+      <c r="O122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/flatfish_box</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>62406</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>빨간 고무대야</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>2762406</v>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>rubber_basin</t>
+        </is>
+      </c>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G123" s="1" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H123" s="1" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I123" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="1" t="n"/>
+      <c r="O123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/rubber_basin</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>62407</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>싯가 가격판</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>2762407</v>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t>market_price</t>
+        </is>
+      </c>
+      <c r="E124" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H124" s="1" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="I124" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" s="1" t="inlineStr">
+        <is>
+          <t>#8fd3e8</t>
+        </is>
+      </c>
+      <c r="O124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/market_price</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>62408</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>노래하는 물고기 장식</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>2762408</v>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>singing_fish</t>
+        </is>
+      </c>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H125" s="1" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I125" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="1" t="n"/>
+      <c r="O125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/singing_fish</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>62409</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>춤추는 꽃게</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>2762409</v>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>crab_rave</t>
+        </is>
+      </c>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G126" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H126" s="1" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I126" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="1" t="n"/>
+      <c r="O126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/crab_rave</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>62410</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>블롭피시 표본병</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>2762410</v>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>blobfish_jar</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G127" s="1" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H127" s="1" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I127" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="1" t="inlineStr">
+        <is>
+          <t>#8fd3e8</t>
+        </is>
+      </c>
+      <c r="O127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/blobfish_jar</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>62411</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>진주 거대 조개</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>2762411</v>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>giant_clam</t>
+        </is>
+      </c>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H128" s="1" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I128" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="1" t="n"/>
+      <c r="O128" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P128" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q128" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R128" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/giant_clam</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>62412</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>경매 1호 황금 참치</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>2762412</v>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>golden_tuna</t>
+        </is>
+      </c>
+      <c r="E129" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G129" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="H129" s="1" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I129" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" s="1" t="n"/>
+      <c r="O129" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P129" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q129" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R129" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/golden_tuna</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>62413</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>다이아몬드 킹크랩</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>2762413</v>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>diamond_crab</t>
+        </is>
+      </c>
+      <c r="E130" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G130" s="1" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H130" s="1" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="I130" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" s="1" t="n"/>
+      <c r="O130" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P130" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q130" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R130" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/diamond_crab</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>63401</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>대형 수조</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>2763401</v>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>f_aquarium</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="G131" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H131" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="1" t="n"/>
+      <c r="O131" s="1" t="n">
+        <v>62401</v>
+      </c>
+      <c r="P131" s="1" t="n">
+        <v>62404</v>
+      </c>
+      <c r="Q131" s="1" t="n">
+        <v>62408</v>
+      </c>
+      <c r="R131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_aquarium</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>63402</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>수산시장 좌판</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>2763402</v>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>f_fish_stall</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="G132" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H132" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="1" t="n"/>
+      <c r="O132" s="1" t="n">
+        <v>62403</v>
+      </c>
+      <c r="P132" s="1" t="n">
+        <v>62406</v>
+      </c>
+      <c r="Q132" s="1" t="n">
+        <v>62410</v>
+      </c>
+      <c r="R132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_fish_stall</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>63403</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>표본 보관장</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>2763403</v>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t>f_specimen_shelf</t>
+        </is>
+      </c>
+      <c r="E133" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="G133" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H133" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I133" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="1" t="n"/>
+      <c r="O133" s="1" t="n">
+        <v>62405</v>
+      </c>
+      <c r="P133" s="1" t="n">
+        <v>62408</v>
+      </c>
+      <c r="Q133" s="1" t="n">
+        <v>62402</v>
+      </c>
+      <c r="R133" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_specimen_shelf</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>63404</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>수산물 냉동고</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>2763404</v>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>f_seafood_freezer</t>
+        </is>
+      </c>
+      <c r="E134" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G134" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H134" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="1" t="n"/>
+      <c r="O134" s="1" t="n">
+        <v>62407</v>
+      </c>
+      <c r="P134" s="1" t="n">
+        <v>62410</v>
+      </c>
+      <c r="Q134" s="1" t="n">
+        <v>62404</v>
+      </c>
+      <c r="R134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_seafood_freezer</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>63405</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>산호 배양 탱크</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>2763405</v>
+      </c>
+      <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t>f_coral_tank</t>
+        </is>
+      </c>
+      <c r="E135" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="G135" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="H135" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I135" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="1" t="n"/>
+      <c r="O135" s="1" t="n">
+        <v>62409</v>
+      </c>
+      <c r="P135" s="1" t="n">
+        <v>62402</v>
+      </c>
+      <c r="Q135" s="1" t="n">
+        <v>62406</v>
+      </c>
+      <c r="R135" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_coral_tank</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>62501</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>철모</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>2762501</v>
+      </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>army_helmet</t>
+        </is>
+      </c>
+      <c r="E136" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G136" s="1" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H136" s="1" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I136" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="1" t="inlineStr">
+        <is>
+          <t>#8a9a6a</t>
+        </is>
+      </c>
+      <c r="O136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/army_helmet</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>62502</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>탄약 상자</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>2762502</v>
+      </c>
+      <c r="D137" s="1" t="inlineStr">
+        <is>
+          <t>ammo_crate</t>
+        </is>
+      </c>
+      <c r="E137" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G137" s="1" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H137" s="1" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I137" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="1" t="n"/>
+      <c r="O137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/ammo_crate</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>62503</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>무전기</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>2762503</v>
+      </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>field_radio</t>
+        </is>
+      </c>
+      <c r="E138" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G138" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H138" s="1" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I138" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="1" t="n"/>
+      <c r="O138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/field_radio</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>62504</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>전투식량</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>2762504</v>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t>ration_tins</t>
+        </is>
+      </c>
+      <c r="E139" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G139" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H139" s="1" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I139" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" s="1" t="inlineStr">
+        <is>
+          <t>#8a9a6a</t>
+        </is>
+      </c>
+      <c r="O139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/ration_tins</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>62505</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>모형 전투기</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>2762505</v>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>model_plane</t>
+        </is>
+      </c>
+      <c r="E140" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H140" s="1" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I140" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="1" t="n"/>
+      <c r="O140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/model_plane</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>62506</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>빨간 드럼통</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>2762506</v>
+      </c>
+      <c r="D141" s="1" t="inlineStr">
+        <is>
+          <t>red_barrel</t>
+        </is>
+      </c>
+      <c r="E141" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G141" s="1" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H141" s="1" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I141" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="1" t="n"/>
+      <c r="O141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/red_barrel</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>62507</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>X 키캡</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>2762507</v>
+      </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>x_keycap</t>
+        </is>
+      </c>
+      <c r="E142" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F142" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G142" s="1" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H142" s="1" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I142" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" s="1" t="inlineStr">
+        <is>
+          <t>#8a9a6a</t>
+        </is>
+      </c>
+      <c r="O142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/x_keycap</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>62508</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>알통 쥐 포스터</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>2762508</v>
+      </c>
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t>flex_poster</t>
+        </is>
+      </c>
+      <c r="E143" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G143" s="1" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H143" s="1" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="I143" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" s="1" t="n"/>
+      <c r="O143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/flex_poster</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>62509</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>손가락 쥐 포스터</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>2762509</v>
+      </c>
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>pointing_poster</t>
+        </is>
+      </c>
+      <c r="E144" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F144" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G144" s="1" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H144" s="1" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I144" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" s="1" t="n"/>
+      <c r="O144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/pointing_poster</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>62510</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>철모 쓴 윌슨</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>2762510</v>
+      </c>
+      <c r="D145" s="1" t="inlineStr">
+        <is>
+          <t>wilson</t>
+        </is>
+      </c>
+      <c r="E145" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F145" s="1" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G145" s="1" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H145" s="1" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I145" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="1" t="inlineStr">
+        <is>
+          <t>#8a9a6a</t>
+        </is>
+      </c>
+      <c r="O145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/wilson</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>62511</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>황금 훈장</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>2762511</v>
+      </c>
+      <c r="D146" s="1" t="inlineStr">
+        <is>
+          <t>gold_medal</t>
+        </is>
+      </c>
+      <c r="E146" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G146" s="1" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H146" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I146" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J146" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" s="1" t="n"/>
+      <c r="O146" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P146" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q146" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R146" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/gold_medal</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>62512</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>낙하산 보급 상자</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>2762512</v>
+      </c>
+      <c r="D147" s="1" t="inlineStr">
+        <is>
+          <t>airdrop_crate</t>
+        </is>
+      </c>
+      <c r="E147" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F147" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G147" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H147" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I147" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J147" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" s="1" t="n"/>
+      <c r="O147" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P147" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q147" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R147" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/airdrop_crate</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>62513</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>순금 프라이팬</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>2762513</v>
+      </c>
+      <c r="D148" s="1" t="inlineStr">
+        <is>
+          <t>golden_pan</t>
+        </is>
+      </c>
+      <c r="E148" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F148" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G148" s="1" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H148" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="I148" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J148" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" s="1" t="n"/>
+      <c r="O148" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P148" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q148" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R148" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/golden_pan</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>63501</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>탄약 창고</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>2763501</v>
+      </c>
+      <c r="D149" s="1" t="inlineStr">
+        <is>
+          <t>f_ammo_depot</t>
+        </is>
+      </c>
+      <c r="E149" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F149" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="G149" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H149" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" s="1" t="n"/>
+      <c r="O149" s="1" t="n">
+        <v>62501</v>
+      </c>
+      <c r="P149" s="1" t="n">
+        <v>62504</v>
+      </c>
+      <c r="Q149" s="1" t="n">
+        <v>62508</v>
+      </c>
+      <c r="R149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_ammo_depot</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>63502</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>작전 지도 테이블</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>2763502</v>
+      </c>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>f_map_table</t>
+        </is>
+      </c>
+      <c r="E150" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="G150" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H150" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I150" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" s="1" t="n"/>
+      <c r="O150" s="1" t="n">
+        <v>62503</v>
+      </c>
+      <c r="P150" s="1" t="n">
+        <v>62506</v>
+      </c>
+      <c r="Q150" s="1" t="n">
+        <v>62510</v>
+      </c>
+      <c r="R150" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_map_table</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>63503</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>야전 취사대</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>2763503</v>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>f_field_kitchen</t>
+        </is>
+      </c>
+      <c r="E151" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F151" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="G151" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H151" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I151" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" s="1" t="n"/>
+      <c r="O151" s="1" t="n">
+        <v>62505</v>
+      </c>
+      <c r="P151" s="1" t="n">
+        <v>62508</v>
+      </c>
+      <c r="Q151" s="1" t="n">
+        <v>62502</v>
+      </c>
+      <c r="R151" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_field_kitchen</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>63504</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>군용 지프</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>2763504</v>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>f_jeep</t>
+        </is>
+      </c>
+      <c r="E152" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F152" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G152" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H152" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I152" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K152" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L152" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" s="1" t="n"/>
+      <c r="O152" s="1" t="n">
+        <v>62507</v>
+      </c>
+      <c r="P152" s="1" t="n">
+        <v>62510</v>
+      </c>
+      <c r="Q152" s="1" t="n">
+        <v>62504</v>
+      </c>
+      <c r="R152" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_jeep</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>63505</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>기념품 가판대</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>2763505</v>
+      </c>
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>f_souvenir_stand</t>
+        </is>
+      </c>
+      <c r="E153" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F153" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="G153" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="H153" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K153" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" s="1" t="n"/>
+      <c r="O153" s="1" t="n">
+        <v>62509</v>
+      </c>
+      <c r="P153" s="1" t="n">
+        <v>62502</v>
+      </c>
+      <c r="Q153" s="1" t="n">
+        <v>62506</v>
+      </c>
+      <c r="R153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_souvenir_stand</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>62601</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>연료통</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>2762601</v>
+      </c>
+      <c r="D154" s="1" t="inlineStr">
+        <is>
+          <t>fuel_can</t>
+        </is>
+      </c>
+      <c r="E154" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F154" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G154" s="1" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H154" s="1" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I154" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" s="1" t="inlineStr">
+        <is>
+          <t>#c7d3e6</t>
+        </is>
+      </c>
+      <c r="O154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/fuel_can</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>62602</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>로켓 모형</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>2762602</v>
+      </c>
+      <c r="D155" s="1" t="inlineStr">
+        <is>
+          <t>rocket_model</t>
+        </is>
+      </c>
+      <c r="E155" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F155" s="1" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G155" s="1" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H155" s="1" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I155" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" s="1" t="n"/>
+      <c r="O155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/rocket_model</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>62603</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>행성 모형</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>2762603</v>
+      </c>
+      <c r="D156" s="1" t="inlineStr">
+        <is>
+          <t>planet_model</t>
+        </is>
+      </c>
+      <c r="E156" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F156" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G156" s="1" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H156" s="1" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="I156" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" s="1" t="n"/>
+      <c r="O156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/planet_model</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>62604</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>동결건조 우주식량</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>2762604</v>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t>space_food</t>
+        </is>
+      </c>
+      <c r="E157" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F157" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G157" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H157" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I157" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" s="1" t="inlineStr">
+        <is>
+          <t>#c7d3e6</t>
+        </is>
+      </c>
+      <c r="O157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/space_food</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>62605</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>은박지 모자</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>2762605</v>
+      </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t>tinfoil_hat</t>
+        </is>
+      </c>
+      <c r="E158" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H158" s="1" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I158" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" s="1" t="n"/>
+      <c r="O158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/tinfoil_hat</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>62606</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>망원경</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>2762606</v>
+      </c>
+      <c r="D159" s="1" t="inlineStr">
+        <is>
+          <t>telescope</t>
+        </is>
+      </c>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" s="1" t="n"/>
+      <c r="O159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/telescope</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>62607</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>위성 안테나</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>2762607</v>
+      </c>
+      <c r="D160" s="1" t="inlineStr">
+        <is>
+          <t>sat_dish</t>
+        </is>
+      </c>
+      <c r="E160" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H160" s="1" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I160" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" s="1" t="inlineStr">
+        <is>
+          <t>#c7d3e6</t>
+        </is>
+      </c>
+      <c r="O160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/sat_dish</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>62608</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>우주 헬멧</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>2762608</v>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>space_helmet</t>
+        </is>
+      </c>
+      <c r="E161" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F161" s="1" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G161" s="1" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H161" s="1" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="I161" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" s="1" t="n"/>
+      <c r="O161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/space_helmet</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>62609</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>휴스턴 직통 전화기</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>2762609</v>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t>houston_phone</t>
+        </is>
+      </c>
+      <c r="E162" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F162" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G162" s="1" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H162" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I162" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" s="1" t="n"/>
+      <c r="O162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/houston_phone</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>62610</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>떡상 관제 모니터</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>2762610</v>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>to_the_moon</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F163" s="1" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G163" s="1" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H163" s="1" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I163" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" s="1" t="inlineStr">
+        <is>
+          <t>#c7d3e6</t>
+        </is>
+      </c>
+      <c r="O163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/to_the_moon</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>62611</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>월석 케이스</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>2762611</v>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>moon_rock</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F164" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G164" s="1" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H164" s="1" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I164" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" s="1" t="n"/>
+      <c r="O164" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P164" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q164" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R164" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/moon_rock</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>62612</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>황금 레코드</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>2762612</v>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>golden_record</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F165" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G165" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="H165" s="1" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I165" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" s="1" t="n"/>
+      <c r="O165" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P165" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q165" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R165" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/golden_record</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>62613</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>모노리스</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>2762613</v>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>monolith</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F166" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="G166" s="1" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H166" s="1" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="I166" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" s="1" t="n"/>
+      <c r="O166" s="1" t="n">
+        <v>60033</v>
+      </c>
+      <c r="P166" s="1" t="n">
+        <v>60034</v>
+      </c>
+      <c r="Q166" s="1" t="n">
+        <v>60035</v>
+      </c>
+      <c r="R166" s="1" t="n">
+        <v>60036</v>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/monolith</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>63601</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>관제 콘솔</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>2763601</v>
+      </c>
+      <c r="D167" s="1" t="inlineStr">
+        <is>
+          <t>f_control_console</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F167" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="G167" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H167" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" s="1" t="n"/>
+      <c r="O167" s="1" t="n">
+        <v>62601</v>
+      </c>
+      <c r="P167" s="1" t="n">
+        <v>62604</v>
+      </c>
+      <c r="Q167" s="1" t="n">
+        <v>62608</v>
+      </c>
+      <c r="R167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_control_console</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>63602</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>발사대</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>2763602</v>
+      </c>
+      <c r="D168" s="1" t="inlineStr">
+        <is>
+          <t>f_launch_pad</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F168" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="G168" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H168" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" s="1" t="n"/>
+      <c r="O168" s="1" t="n">
+        <v>62603</v>
+      </c>
+      <c r="P168" s="1" t="n">
+        <v>62606</v>
+      </c>
+      <c r="Q168" s="1" t="n">
+        <v>62610</v>
+      </c>
+      <c r="R168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_launch_pad</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>63603</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>무중력 훈련 캡슐</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>2763603</v>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>f_zerog_capsule</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F169" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="G169" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H169" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K169" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" s="1" t="n"/>
+      <c r="O169" s="1" t="n">
+        <v>62605</v>
+      </c>
+      <c r="P169" s="1" t="n">
+        <v>62608</v>
+      </c>
+      <c r="Q169" s="1" t="n">
+        <v>62602</v>
+      </c>
+      <c r="R169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_zerog_capsule</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>63604</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>천체투영기</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>2763604</v>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>f_planetarium</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F170" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G170" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="H170" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" s="1" t="n"/>
+      <c r="O170" s="1" t="n">
+        <v>62607</v>
+      </c>
+      <c r="P170" s="1" t="n">
+        <v>62610</v>
+      </c>
+      <c r="Q170" s="1" t="n">
+        <v>62604</v>
+      </c>
+      <c r="R170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_planetarium</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>63605</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>인터스텔라 책장</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>2763605</v>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>f_tesseract_shelf</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F171" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="G171" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="H171" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="I171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" s="1" t="n"/>
+      <c r="O171" s="1" t="n">
+        <v>62609</v>
+      </c>
+      <c r="P171" s="1" t="n">
+        <v>62602</v>
+      </c>
+      <c r="Q171" s="1" t="n">
+        <v>62606</v>
+      </c>
+      <c r="R171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>Expansion/Items/f_tesseract_shelf</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5320,7 +13408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5374,6 +13462,11 @@
           <t>바닥 색조</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>가구 테마 (쉼표)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -5406,6 +13499,11 @@
           <t>tint</t>
         </is>
       </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>themes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -5434,6 +13532,11 @@
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -5460,6 +13563,11 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lab,Office,Breakroom,Nap,Storage</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -5482,6 +13590,11 @@
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lab,Office,Breakroom,Nap,Storage</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -5508,6 +13621,11 @@
           <t>rgba(157,213,168,.16)</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lab,Office,Breakroom,Nap,Storage</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -5534,6 +13652,11 @@
           <t>rgba(143,179,199,.2)</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lab,Office,Breakroom,Nap,Storage</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -5541,14 +13664,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>연구소장 층</t>
+          <t>고양이 연구소</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>2870005</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
@@ -5558,6 +13681,146 @@
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>rgba(227,196,106,.18)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cat_A,Cat_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>70006</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>지구과학 연구소</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2870006</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dino_A,Dino_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>70007</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>연구소 확장 공사 현장</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2870007</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Build_A,Build_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>70008</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>수중 연구소</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2870008</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sea_A,Sea_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>70009</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2차대전 박물관</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2870009</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>War_A,War_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>70010</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>우주 연구소</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2870010</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Space_A,Space_B</t>
         </is>
       </c>
     </row>
@@ -5572,7 +13835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6271,6 +14534,1146 @@
         <v>0.64</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>80101</v>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>Cat_A</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>63101</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>80102</v>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>Cat_A</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>63102</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>80103</v>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>Cat_A</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>63104</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>80104</v>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>Cat_A</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>63103</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>80105</v>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>Cat_A</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>63105</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>80106</v>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Cat_B</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>63102</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>80107</v>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Cat_B</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>63105</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>80108</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Cat_B</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>63101</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>80109</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Cat_B</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>63104</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>80110</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>Cat_B</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>63103</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>80111</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>Dino_A</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>63201</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>80112</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>Dino_A</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>63202</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>80113</v>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>Dino_A</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>63204</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>80114</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>Dino_A</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>63203</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>80115</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>Dino_A</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>63205</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>80116</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>Dino_B</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>63202</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>80117</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>Dino_B</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>63205</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>80118</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Dino_B</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>63201</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>80119</v>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>Dino_B</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>63204</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>80120</v>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>Dino_B</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>63203</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>80121</v>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>Build_A</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>63301</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>80122</v>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Build_A</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>63302</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>80123</v>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Build_A</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>63304</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>80124</v>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Build_A</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>63303</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>80125</v>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>Build_A</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>63305</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>80126</v>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Build_B</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>63302</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>80127</v>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>Build_B</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>63305</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>80128</v>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>Build_B</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>63301</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>80129</v>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>Build_B</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>63304</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>80130</v>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>Build_B</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>63303</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>80131</v>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Sea_A</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>63401</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>80132</v>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Sea_A</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>63402</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>80133</v>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>Sea_A</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>63404</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>80134</v>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>Sea_A</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>63403</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>80135</v>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>Sea_A</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>63405</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>80136</v>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>Sea_B</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>63402</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>80137</v>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>Sea_B</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>63405</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>80138</v>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>Sea_B</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>63401</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>80139</v>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>Sea_B</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>63404</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>80140</v>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>Sea_B</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>63403</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>80141</v>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>War_A</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>63501</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>80142</v>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>War_A</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>63502</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>80143</v>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>War_A</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>63504</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>80144</v>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>War_A</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>63503</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>80145</v>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>War_A</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>63505</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>80146</v>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>War_B</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>63502</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80147</v>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>War_B</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>63505</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>80148</v>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>War_B</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>63501</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>80149</v>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>War_B</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>63504</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>80150</v>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>War_B</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>63503</v>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>80151</v>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>Space_A</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>63601</v>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>80152</v>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>Space_A</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>63602</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>80153</v>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>Space_A</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>63604</v>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>80154</v>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>Space_A</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>63603</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>80155</v>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>Space_A</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>63605</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>80156</v>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>Space_B</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>63602</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>80157</v>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>Space_B</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>63605</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>80158</v>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>Space_B</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>63601</v>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>80159</v>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>Space_B</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>63604</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>80160</v>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>Space_B</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>63603</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/물건 테이블.xlsx
+++ b/Data_Table/물건 테이블.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Item" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Zone" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Furniture_Layout" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zone" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Furniture_Layout" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
